--- a/labeled/Add_Eating/July/multi_seed_results/all_seeds_summary.xlsx
+++ b/labeled/Add_Eating/July/multi_seed_results/all_seeds_summary.xlsx
@@ -485,159 +485,159 @@
         <v>404</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9576502442359924</v>
+        <v>0.908056378364563</v>
       </c>
       <c r="C2" t="n">
-        <v>25.22818183898926</v>
+        <v>53.13963317871094</v>
       </c>
       <c r="D2" t="n">
-        <v>5.022766590118408</v>
+        <v>7.289693832397461</v>
       </c>
       <c r="E2" t="n">
-        <v>68.41844940185547</v>
+        <v>232.4483947753906</v>
       </c>
       <c r="F2" t="n">
-        <v>2367</v>
+        <v>1469</v>
       </c>
       <c r="G2" t="n">
-        <v>592</v>
+        <v>368</v>
       </c>
       <c r="H2" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="I2" t="n">
-        <v>3104</v>
+        <v>1930</v>
       </c>
       <c r="J2" t="n">
-        <v>3.299168975069252</v>
+        <v>3.150537634408602</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9525960683822632</v>
+        <v>0.812682569026947</v>
       </c>
       <c r="C3" t="n">
-        <v>32.02988433837891</v>
+        <v>52.9435920715332</v>
       </c>
       <c r="D3" t="n">
-        <v>5.659494876861572</v>
+        <v>7.27623462677002</v>
       </c>
       <c r="E3" t="n">
-        <v>53.53107452392578</v>
+        <v>149.4904937744141</v>
       </c>
       <c r="F3" t="n">
-        <v>2367</v>
+        <v>1469</v>
       </c>
       <c r="G3" t="n">
-        <v>592</v>
+        <v>368</v>
       </c>
       <c r="H3" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="I3" t="n">
-        <v>3104</v>
+        <v>1930</v>
       </c>
       <c r="J3" t="n">
-        <v>3.299168975069252</v>
+        <v>3.150537634408602</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9522639513015747</v>
+        <v>0.7890843152999878</v>
       </c>
       <c r="C4" t="n">
-        <v>29.37298583984375</v>
+        <v>70.81519317626953</v>
       </c>
       <c r="D4" t="n">
-        <v>5.419684886932373</v>
+        <v>8.415176391601562</v>
       </c>
       <c r="E4" t="n">
-        <v>53.36138153076172</v>
+        <v>62.30463409423828</v>
       </c>
       <c r="F4" t="n">
-        <v>2367</v>
+        <v>1469</v>
       </c>
       <c r="G4" t="n">
-        <v>592</v>
+        <v>368</v>
       </c>
       <c r="H4" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="I4" t="n">
-        <v>3104</v>
+        <v>1930</v>
       </c>
       <c r="J4" t="n">
-        <v>3.299168975069252</v>
+        <v>3.150537634408602</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>303</v>
+        <v>505</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9479125738143921</v>
+        <v>0.7524206638336182</v>
       </c>
       <c r="C5" t="n">
-        <v>32.541748046875</v>
+        <v>60.70269393920898</v>
       </c>
       <c r="D5" t="n">
-        <v>5.704537391662598</v>
+        <v>7.79119348526001</v>
       </c>
       <c r="E5" t="n">
-        <v>60.21710205078125</v>
+        <v>314.0543823242188</v>
       </c>
       <c r="F5" t="n">
-        <v>2367</v>
+        <v>1469</v>
       </c>
       <c r="G5" t="n">
-        <v>592</v>
+        <v>368</v>
       </c>
       <c r="H5" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="I5" t="n">
-        <v>3104</v>
+        <v>1930</v>
       </c>
       <c r="J5" t="n">
-        <v>3.299168975069252</v>
+        <v>3.150537634408602</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>505</v>
+        <v>789</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9252322912216187</v>
+        <v>0.7376039624214172</v>
       </c>
       <c r="C6" t="n">
-        <v>44.27427291870117</v>
+        <v>69.92232513427734</v>
       </c>
       <c r="D6" t="n">
-        <v>6.653891563415527</v>
+        <v>8.361956596374512</v>
       </c>
       <c r="E6" t="n">
-        <v>94.92898559570312</v>
+        <v>61.09257507324219</v>
       </c>
       <c r="F6" t="n">
-        <v>2367</v>
+        <v>1469</v>
       </c>
       <c r="G6" t="n">
-        <v>592</v>
+        <v>368</v>
       </c>
       <c r="H6" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="I6" t="n">
-        <v>3104</v>
+        <v>1930</v>
       </c>
       <c r="J6" t="n">
-        <v>3.299168975069252</v>
+        <v>3.150537634408602</v>
       </c>
     </row>
     <row r="7">
@@ -645,95 +645,95 @@
         <v>456</v>
       </c>
       <c r="B7" t="n">
-        <v>0.919154167175293</v>
+        <v>0.7146018743515015</v>
       </c>
       <c r="C7" t="n">
-        <v>48.78376770019531</v>
+        <v>111.9356384277344</v>
       </c>
       <c r="D7" t="n">
-        <v>6.984537601470947</v>
+        <v>10.57996368408203</v>
       </c>
       <c r="E7" t="n">
-        <v>53.39549255371094</v>
+        <v>321.9391479492188</v>
       </c>
       <c r="F7" t="n">
-        <v>2367</v>
+        <v>1469</v>
       </c>
       <c r="G7" t="n">
-        <v>592</v>
+        <v>368</v>
       </c>
       <c r="H7" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="I7" t="n">
-        <v>3104</v>
+        <v>1930</v>
       </c>
       <c r="J7" t="n">
-        <v>3.299168975069252</v>
+        <v>3.150537634408602</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>789</v>
+        <v>202</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9067713618278503</v>
+        <v>0.668702244758606</v>
       </c>
       <c r="C8" t="n">
-        <v>55.10331344604492</v>
+        <v>122.4956436157227</v>
       </c>
       <c r="D8" t="n">
-        <v>7.423160552978516</v>
+        <v>11.06777477264404</v>
       </c>
       <c r="E8" t="n">
-        <v>59.15432739257812</v>
+        <v>151.6923217773438</v>
       </c>
       <c r="F8" t="n">
-        <v>2367</v>
+        <v>1469</v>
       </c>
       <c r="G8" t="n">
-        <v>592</v>
+        <v>368</v>
       </c>
       <c r="H8" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="I8" t="n">
-        <v>3104</v>
+        <v>1930</v>
       </c>
       <c r="J8" t="n">
-        <v>3.299168975069252</v>
+        <v>3.150537634408602</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>202</v>
+        <v>42</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9066396951675415</v>
+        <v>0.6538398265838623</v>
       </c>
       <c r="C9" t="n">
-        <v>52.85093307495117</v>
+        <v>104.7745819091797</v>
       </c>
       <c r="D9" t="n">
-        <v>7.269864559173584</v>
+        <v>10.23594570159912</v>
       </c>
       <c r="E9" t="n">
-        <v>43.09491729736328</v>
+        <v>100.1020660400391</v>
       </c>
       <c r="F9" t="n">
-        <v>2367</v>
+        <v>1469</v>
       </c>
       <c r="G9" t="n">
-        <v>592</v>
+        <v>368</v>
       </c>
       <c r="H9" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="I9" t="n">
-        <v>3104</v>
+        <v>1930</v>
       </c>
       <c r="J9" t="n">
-        <v>3.299168975069252</v>
+        <v>3.150537634408602</v>
       </c>
     </row>
     <row r="10">
@@ -741,63 +741,63 @@
         <v>606</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9049498438835144</v>
+        <v>0.5379631519317627</v>
       </c>
       <c r="C10" t="n">
-        <v>71.53227233886719</v>
+        <v>247.4944000244141</v>
       </c>
       <c r="D10" t="n">
-        <v>8.457674980163574</v>
+        <v>15.73195457458496</v>
       </c>
       <c r="E10" t="n">
-        <v>68.00521850585938</v>
+        <v>124.9829177856445</v>
       </c>
       <c r="F10" t="n">
-        <v>2367</v>
+        <v>1469</v>
       </c>
       <c r="G10" t="n">
-        <v>592</v>
+        <v>368</v>
       </c>
       <c r="H10" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="I10" t="n">
-        <v>3104</v>
+        <v>1930</v>
       </c>
       <c r="J10" t="n">
-        <v>3.299168975069252</v>
+        <v>3.150537634408602</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>42</v>
+        <v>303</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8980578184127808</v>
+        <v>0.4768520593643188</v>
       </c>
       <c r="C11" t="n">
-        <v>58.34581756591797</v>
+        <v>117.1729278564453</v>
       </c>
       <c r="D11" t="n">
-        <v>7.638443470001221</v>
+        <v>10.82464408874512</v>
       </c>
       <c r="E11" t="n">
-        <v>47.30894470214844</v>
+        <v>87.53803253173828</v>
       </c>
       <c r="F11" t="n">
-        <v>2367</v>
+        <v>1469</v>
       </c>
       <c r="G11" t="n">
-        <v>592</v>
+        <v>368</v>
       </c>
       <c r="H11" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="I11" t="n">
-        <v>3104</v>
+        <v>1930</v>
       </c>
       <c r="J11" t="n">
-        <v>3.299168975069252</v>
+        <v>3.150537634408602</v>
       </c>
     </row>
   </sheetData>
